--- a/Gantt_Cutover_Colombia_GoLive_09Nov_v12.xlsx
+++ b/Gantt_Cutover_Colombia_GoLive_09Nov_v12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pjypl-my.sharepoint.com/personal/gsalinas_pjportland_cl/Documents/_AutomationUI/Gantt/RetroPlanning/Colombia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_DFCE136AB520F1D52948A74420099101C53FFB62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E21F04-281A-476E-B327-2C7418BB1EB3}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_DFCE136AB520F1D52948A74420099101C53FFB62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59D7BEB3-29CB-487D-A673-A7027A95881B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="33015" yWindow="2700" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt Cutover" sheetId="1" r:id="rId1"/>
@@ -5078,11 +5078,11 @@
         <v>6</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N22" s="13" t="str">
         <f ca="1">IF(M22="Finalizado","",IF(K22&lt;Hoy!$C$4,"Vencida",IF(AND(J22&lt;=Hoy!$C$4,M22="No iniciado"),"Sin iniciar","")))</f>
-        <v>Sin iniciar</v>
+        <v/>
       </c>
       <c r="O22" s="18"/>
       <c r="P22" s="19" t="str">
@@ -5466,11 +5466,11 @@
         <v>7</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N24" s="13" t="str">
         <f ca="1">IF(M24="Finalizado","",IF(K24&lt;Hoy!$C$4,"Vencida",IF(AND(J24&lt;=Hoy!$C$4,M24="No iniciado"),"Sin iniciar","")))</f>
-        <v>Sin iniciar</v>
+        <v/>
       </c>
       <c r="O24" s="18"/>
       <c r="P24" s="19" t="str">
@@ -6788,11 +6788,11 @@
         <v>2</v>
       </c>
       <c r="M32" s="17" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N32" s="13" t="str">
         <f ca="1">IF(M32="Finalizado","",IF(K32&lt;Hoy!$C$4,"Vencida",IF(AND(J32&lt;=Hoy!$C$4,M32="No iniciado"),"Sin iniciar","")))</f>
-        <v>Sin iniciar</v>
+        <v/>
       </c>
       <c r="O32" s="18"/>
       <c r="P32" s="19" t="str">
@@ -6982,11 +6982,11 @@
         <v>2</v>
       </c>
       <c r="M33" s="17" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N33" s="13" t="str">
         <f ca="1">IF(M33="Finalizado","",IF(K33&lt;Hoy!$C$4,"Vencida",IF(AND(J33&lt;=Hoy!$C$4,M33="No iniciado"),"Sin iniciar","")))</f>
-        <v>Sin iniciar</v>
+        <v/>
       </c>
       <c r="O33" s="18"/>
       <c r="P33" s="19" t="str">
@@ -7176,11 +7176,11 @@
         <v>2</v>
       </c>
       <c r="M34" s="17" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N34" s="13" t="str">
         <f ca="1">IF(M34="Finalizado","",IF(K34&lt;Hoy!$C$4,"Vencida",IF(AND(J34&lt;=Hoy!$C$4,M34="No iniciado"),"Sin iniciar","")))</f>
-        <v>Sin iniciar</v>
+        <v/>
       </c>
       <c r="O34" s="18"/>
       <c r="P34" s="19" t="str">
@@ -7370,11 +7370,11 @@
         <v>2</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N35" s="13" t="str">
         <f ca="1">IF(M35="Finalizado","",IF(K35&lt;Hoy!$C$4,"Vencida",IF(AND(J35&lt;=Hoy!$C$4,M35="No iniciado"),"Sin iniciar","")))</f>
-        <v>Sin iniciar</v>
+        <v/>
       </c>
       <c r="O35" s="18"/>
       <c r="P35" s="19" t="str">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="D6" s="30">
         <f>COUNTIFS('Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"En curso")</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E6" s="30">
         <f>COUNTIFS('Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"Demorado")</f>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="F6" s="30">
         <f>COUNTIFS('Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"No iniciado")</f>
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G6" s="30">
         <f ca="1">COUNTIF('Gantt Cutover'!$N$6:$N$61,"Vencida")</f>
@@ -12553,11 +12553,11 @@
       </c>
       <c r="F13" s="35">
         <f>COUNTIFS('Gantt Cutover'!$B$6:$B$61,$B13,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"No iniciado")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="35">
         <f>COUNTIFS('Gantt Cutover'!$B$6:$B$61,$B13,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"En curso")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" s="35">
         <f>COUNTIFS('Gantt Cutover'!$B$6:$B$61,$B13,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"Demorado")</f>
@@ -12643,11 +12643,11 @@
       </c>
       <c r="F15" s="35">
         <f>COUNTIFS('Gantt Cutover'!$B$6:$B$61,$B15,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"No iniciado")</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G15" s="35">
         <f>COUNTIFS('Gantt Cutover'!$B$6:$B$61,$B15,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"En curso")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="35">
         <f>COUNTIFS('Gantt Cutover'!$B$6:$B$61,$B15,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"Demorado")</f>
@@ -13232,11 +13232,11 @@
       </c>
       <c r="D40" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B40,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"No iniciado")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B40,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"En curso")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B40,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"Demorado")</f>
@@ -13261,11 +13261,11 @@
       </c>
       <c r="D41" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B41,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"No iniciado")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B41,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"En curso")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B41,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"Demorado")</f>
@@ -13319,11 +13319,11 @@
       </c>
       <c r="D43" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B43,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"No iniciado")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E43" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B43,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"En curso")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F43" s="40">
         <f>COUNTIFS('Gantt Cutover'!$F$6:$F$61,$B43,'Gantt Cutover'!$D$6:$D$61,"&lt;&gt;Fase",'Gantt Cutover'!$M$6:$M$61,"Demorado")</f>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="L16" s="48" t="str">
         <f ca="1">IFERROR(INDEX('Gantt Cutover'!$M$6:$M$61,MATCH(3,'Gantt Cutover'!$AY$6:$AY$61,0)),"")</f>
-        <v>No iniciado</v>
+        <v>En curso</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="L17" s="48" t="str">
         <f ca="1">IFERROR(INDEX('Gantt Cutover'!$M$6:$M$61,MATCH(4,'Gantt Cutover'!$AY$6:$AY$61,0)),"")</f>
-        <v>No iniciado</v>
+        <v>En curso</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="L18" s="48" t="str">
         <f ca="1">IFERROR(INDEX('Gantt Cutover'!$M$6:$M$61,MATCH(5,'Gantt Cutover'!$AY$6:$AY$61,0)),"")</f>
-        <v>No iniciado</v>
+        <v>En curso</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="L19" s="48" t="str">
         <f ca="1">IFERROR(INDEX('Gantt Cutover'!$M$6:$M$61,MATCH(6,'Gantt Cutover'!$AY$6:$AY$61,0)),"")</f>
-        <v>No iniciado</v>
+        <v>En curso</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="L20" s="48" t="str">
         <f ca="1">IFERROR(INDEX('Gantt Cutover'!$M$6:$M$61,MATCH(7,'Gantt Cutover'!$AY$6:$AY$61,0)),"")</f>
-        <v>No iniciado</v>
+        <v>En curso</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="L21" s="48" t="str">
         <f ca="1">IFERROR(INDEX('Gantt Cutover'!$M$6:$M$61,MATCH(8,'Gantt Cutover'!$AY$6:$AY$61,0)),"")</f>
-        <v>No iniciado</v>
+        <v>En curso</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
